--- a/public/assets/documents/excel/sample_upload/Venue.xlsx
+++ b/public/assets/documents/excel/sample_upload/Venue.xlsx
@@ -33,24 +33,6 @@
   </si>
   <si>
     <t>Projector/LCD Availability</t>
-  </si>
-  <si>
-    <t>Name one</t>
-  </si>
-  <si>
-    <t>unit I</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Name two</t>
-  </si>
-  <si>
-    <t>unit II</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -381,38 +363,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
